--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ140"/>
+  <dimension ref="A1:AZ142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3684,7 +3684,7 @@
         <v>129494887</v>
       </c>
       <c r="B26" t="n">
-        <v>93418</v>
+        <v>93421</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -9281,10 +9281,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129442624</v>
+        <v>136520715</v>
       </c>
       <c r="B72" t="n">
-        <v>8455</v>
+        <v>58162</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9292,37 +9292,46 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>513373</v>
+        <v>513186</v>
       </c>
       <c r="R72" t="n">
-        <v>6733158</v>
+        <v>6733152</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9346,27 +9355,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På ståga</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9381,24 +9385,24 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129442624</t>
+          <t>https://artportalen.se/Sighting/136520715</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129468353</v>
+        <v>129442624</v>
       </c>
       <c r="B73" t="n">
         <v>8455</v>
@@ -9427,25 +9431,16 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>513119</v>
+        <v>513373</v>
       </c>
       <c r="R73" t="n">
-        <v>6733206</v>
+        <v>6733158</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9472,22 +9467,27 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På ståga</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9496,7 +9496,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -9514,13 +9513,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129468353</t>
+          <t>https://artportalen.se/Sighting/129442624</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129482998</v>
+        <v>129468353</v>
       </c>
       <c r="B74" t="n">
         <v>8455</v>
@@ -9552,7 +9551,11 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9560,10 +9563,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>513288</v>
+        <v>513119</v>
       </c>
       <c r="R74" t="n">
-        <v>6733220</v>
+        <v>6733206</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9590,22 +9593,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9632,13 +9635,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129482998</t>
+          <t>https://artportalen.se/Sighting/129468353</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129483526</v>
+        <v>129482998</v>
       </c>
       <c r="B75" t="n">
         <v>8455</v>
@@ -9678,10 +9681,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>513283</v>
+        <v>513288</v>
       </c>
       <c r="R75" t="n">
-        <v>6733204</v>
+        <v>6733220</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9713,7 +9716,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9723,12 +9726,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ståga tall m Spillkråk</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9755,13 +9753,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129483526</t>
+          <t>https://artportalen.se/Sighting/129482998</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129490326</v>
+        <v>129483526</v>
       </c>
       <c r="B76" t="n">
         <v>8455</v>
@@ -9801,10 +9799,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>513307</v>
+        <v>513283</v>
       </c>
       <c r="R76" t="n">
-        <v>6733066</v>
+        <v>6733204</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9836,7 +9834,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9846,7 +9844,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ståga tall m Spillkråk</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9859,16 +9862,6 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>Myrholme,ca 20m bred och 80m lång.</t>
-        </is>
-      </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
@@ -9883,13 +9876,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129490326</t>
+          <t>https://artportalen.se/Sighting/129483526</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129490370</v>
+        <v>129490326</v>
       </c>
       <c r="B77" t="n">
         <v>8455</v>
@@ -9929,10 +9922,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>513314</v>
+        <v>513307</v>
       </c>
       <c r="R77" t="n">
-        <v>6733062</v>
+        <v>6733066</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9964,7 +9957,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9974,7 +9967,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9994,7 +9987,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Myrholme, ca 20m bred och 80m lång, kalkbarrskog</t>
+          <t>Myrholme,ca 20m bred och 80m lång.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10011,13 +10004,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129490370</t>
+          <t>https://artportalen.se/Sighting/129490326</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129493485</v>
+        <v>129490370</v>
       </c>
       <c r="B78" t="n">
         <v>8455</v>
@@ -10046,16 +10039,21 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>513317</v>
+        <v>513314</v>
       </c>
       <c r="R78" t="n">
-        <v>6733046</v>
+        <v>6733062</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10087,7 +10085,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10097,7 +10095,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10106,8 +10104,19 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Myrholme, ca 20m bred och 80m lång, kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -10123,13 +10132,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129493485</t>
+          <t>https://artportalen.se/Sighting/129490370</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129495523</v>
+        <v>129493485</v>
       </c>
       <c r="B79" t="n">
         <v>8455</v>
@@ -10164,10 +10173,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>513319</v>
+        <v>513317</v>
       </c>
       <c r="R79" t="n">
-        <v>6733151</v>
+        <v>6733046</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10199,7 +10208,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10209,7 +10218,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10235,16 +10244,16 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129495523</t>
+          <t>https://artportalen.se/Sighting/129493485</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133345742</v>
+        <v>129495523</v>
       </c>
       <c r="B80" t="n">
-        <v>8460</v>
+        <v>8455</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10270,21 +10279,16 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lögkarlsmyra, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>513216</v>
+        <v>513319</v>
       </c>
       <c r="R80" t="n">
-        <v>6732971</v>
+        <v>6733151</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10311,27 +10315,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>död stående tall med mycket hänglav på.</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10340,7 +10339,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -10358,62 +10356,59 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133345742</t>
+          <t>https://artportalen.se/Sighting/129495523</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>104217709</v>
+        <v>133345742</v>
       </c>
       <c r="B81" t="n">
-        <v>99118</v>
+        <v>8460</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Falun, Dlr</t>
+          <t>Lögkarlsmyra, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>513180</v>
+        <v>513216</v>
       </c>
       <c r="R81" t="n">
-        <v>6733144</v>
+        <v>6732971</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10437,27 +10432,27 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>ca 20 exemplar, större och mindre.</t>
+          <t>död stående tall med mycket hänglav på.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10484,66 +10479,63 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104217709</t>
+          <t>https://artportalen.se/Sighting/133345742</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129464509</v>
+        <v>136525638</v>
       </c>
       <c r="B82" t="n">
-        <v>99118</v>
+        <v>58870</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>513193</v>
+        <v>513186</v>
       </c>
       <c r="R82" t="n">
-        <v>6733222</v>
+        <v>6733152</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10567,22 +10559,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10591,31 +10583,30 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129464509</t>
+          <t>https://artportalen.se/Sighting/136525638</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129464731</v>
+        <v>104217709</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -10645,30 +10636,26 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Falun, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>513185</v>
+        <v>513180</v>
       </c>
       <c r="R83" t="n">
-        <v>6733220</v>
+        <v>6733144</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10692,27 +10679,27 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>En blomställning</t>
+          <t>ca 20 exemplar, större och mindre.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10739,13 +10726,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129464731</t>
+          <t>https://artportalen.se/Sighting/104217709</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129464900</v>
+        <v>129464509</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -10775,7 +10762,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10792,10 +10779,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>513183</v>
+        <v>513193</v>
       </c>
       <c r="R84" t="n">
-        <v>6733215</v>
+        <v>6733222</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10827,7 +10814,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10837,7 +10824,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10864,13 +10851,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129464900</t>
+          <t>https://artportalen.se/Sighting/129464509</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129465000</v>
+        <v>129464731</v>
       </c>
       <c r="B85" t="n">
         <v>99118</v>
@@ -10900,7 +10887,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10917,10 +10904,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>513179</v>
+        <v>513185</v>
       </c>
       <c r="R85" t="n">
-        <v>6733217</v>
+        <v>6733220</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10952,7 +10939,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10962,7 +10949,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10989,13 +10981,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129465000</t>
+          <t>https://artportalen.se/Sighting/129464731</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129465138</v>
+        <v>129464900</v>
       </c>
       <c r="B86" t="n">
         <v>99118</v>
@@ -11025,7 +11017,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11042,10 +11034,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>513177</v>
+        <v>513183</v>
       </c>
       <c r="R86" t="n">
-        <v>6733214</v>
+        <v>6733215</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11077,7 +11069,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11087,7 +11079,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11114,13 +11106,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129465138</t>
+          <t>https://artportalen.se/Sighting/129464900</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129465776</v>
+        <v>129465000</v>
       </c>
       <c r="B87" t="n">
         <v>99118</v>
@@ -11150,7 +11142,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>67</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11167,10 +11159,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>513177</v>
+        <v>513179</v>
       </c>
       <c r="R87" t="n">
-        <v>6733204</v>
+        <v>6733217</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11202,7 +11194,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11212,7 +11204,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11239,13 +11231,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129465776</t>
+          <t>https://artportalen.se/Sighting/129465000</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129466275</v>
+        <v>129465138</v>
       </c>
       <c r="B88" t="n">
         <v>99118</v>
@@ -11275,7 +11267,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11288,14 +11280,14 @@
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lögkarlsmyren, Lögkarlsmyren, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
         <v>513177</v>
       </c>
       <c r="R88" t="n">
-        <v>6733178</v>
+        <v>6733214</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11327,7 +11319,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11337,7 +11329,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11364,13 +11356,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129466275</t>
+          <t>https://artportalen.se/Sighting/129465138</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129466413</v>
+        <v>129465776</v>
       </c>
       <c r="B89" t="n">
         <v>99118</v>
@@ -11400,7 +11392,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11413,14 +11405,14 @@
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lögkarlsmyren, Lögkarlsmyren, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>513167</v>
+        <v>513177</v>
       </c>
       <c r="R89" t="n">
-        <v>6733186</v>
+        <v>6733204</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11452,7 +11444,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11462,7 +11454,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11489,13 +11481,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129466413</t>
+          <t>https://artportalen.se/Sighting/129465776</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129466484</v>
+        <v>129466275</v>
       </c>
       <c r="B90" t="n">
         <v>99118</v>
@@ -11525,7 +11517,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11542,10 +11534,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>513165</v>
+        <v>513177</v>
       </c>
       <c r="R90" t="n">
-        <v>6733182</v>
+        <v>6733178</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11577,7 +11569,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11587,7 +11579,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11614,13 +11606,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129466484</t>
+          <t>https://artportalen.se/Sighting/129466275</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129466579</v>
+        <v>129466413</v>
       </c>
       <c r="B91" t="n">
         <v>99118</v>
@@ -11650,7 +11642,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11667,10 +11659,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>513164</v>
+        <v>513167</v>
       </c>
       <c r="R91" t="n">
-        <v>6733189</v>
+        <v>6733186</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11702,7 +11694,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11712,7 +11704,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11739,13 +11731,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129466579</t>
+          <t>https://artportalen.se/Sighting/129466413</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129466678</v>
+        <v>129466484</v>
       </c>
       <c r="B92" t="n">
         <v>99118</v>
@@ -11775,7 +11767,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11788,11 +11780,11 @@
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarlsmyren, Lögkarlsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>513153</v>
+        <v>513165</v>
       </c>
       <c r="R92" t="n">
         <v>6733182</v>
@@ -11827,7 +11819,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11837,7 +11829,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11864,13 +11856,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129466678</t>
+          <t>https://artportalen.se/Sighting/129466484</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129466851</v>
+        <v>129466579</v>
       </c>
       <c r="B93" t="n">
         <v>99118</v>
@@ -11913,14 +11905,14 @@
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarlsmyren, Lögkarlsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>513145</v>
+        <v>513164</v>
       </c>
       <c r="R93" t="n">
-        <v>6733185</v>
+        <v>6733189</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11952,7 +11944,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11962,7 +11954,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11989,13 +11981,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129466851</t>
+          <t>https://artportalen.se/Sighting/129466579</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129466898</v>
+        <v>129466678</v>
       </c>
       <c r="B94" t="n">
         <v>99118</v>
@@ -12025,7 +12017,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -12042,10 +12034,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>513147</v>
+        <v>513153</v>
       </c>
       <c r="R94" t="n">
-        <v>6733183</v>
+        <v>6733182</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12077,7 +12069,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12087,7 +12079,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12114,13 +12106,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129466898</t>
+          <t>https://artportalen.se/Sighting/129466678</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129466948</v>
+        <v>129466851</v>
       </c>
       <c r="B95" t="n">
         <v>99118</v>
@@ -12150,7 +12142,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -12167,10 +12159,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>513144</v>
+        <v>513145</v>
       </c>
       <c r="R95" t="n">
-        <v>6733188</v>
+        <v>6733185</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12202,7 +12194,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12212,7 +12204,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12239,13 +12231,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129466948</t>
+          <t>https://artportalen.se/Sighting/129466851</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129467138</v>
+        <v>129466898</v>
       </c>
       <c r="B96" t="n">
         <v>99118</v>
@@ -12275,19 +12267,27 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>513142</v>
+        <v>513147</v>
       </c>
       <c r="R96" t="n">
-        <v>6733192</v>
+        <v>6733183</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12319,7 +12319,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12338,6 +12338,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -12355,13 +12356,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129467138</t>
+          <t>https://artportalen.se/Sighting/129466898</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129467585</v>
+        <v>129466948</v>
       </c>
       <c r="B97" t="n">
         <v>99118</v>
@@ -12391,7 +12392,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -12408,10 +12409,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>513130</v>
+        <v>513144</v>
       </c>
       <c r="R97" t="n">
-        <v>6733196</v>
+        <v>6733188</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12443,7 +12444,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12453,7 +12454,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12480,13 +12481,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129467585</t>
+          <t>https://artportalen.se/Sighting/129466948</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129471145</v>
+        <v>129467138</v>
       </c>
       <c r="B98" t="n">
         <v>99118</v>
@@ -12516,27 +12517,19 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Lögkarlsmyren, Lögkarlsmyren, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>513106</v>
+        <v>513142</v>
       </c>
       <c r="R98" t="n">
-        <v>6733237</v>
+        <v>6733192</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12568,7 +12561,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12578,7 +12571,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12587,7 +12580,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -12605,13 +12597,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129471145</t>
+          <t>https://artportalen.se/Sighting/129467138</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129472963</v>
+        <v>129467585</v>
       </c>
       <c r="B99" t="n">
         <v>99118</v>
@@ -12641,7 +12633,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -12654,14 +12646,14 @@
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lögkarlsmyren, Lögkarlsmyren, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>513140</v>
+        <v>513130</v>
       </c>
       <c r="R99" t="n">
-        <v>6733188</v>
+        <v>6733196</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12693,7 +12685,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12703,7 +12695,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12730,13 +12722,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129472963</t>
+          <t>https://artportalen.se/Sighting/129467585</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129483716</v>
+        <v>129471145</v>
       </c>
       <c r="B100" t="n">
         <v>99118</v>
@@ -12766,7 +12758,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12779,14 +12771,14 @@
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarlsmyren, Lögkarlsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>513273</v>
+        <v>513106</v>
       </c>
       <c r="R100" t="n">
-        <v>6733194</v>
+        <v>6733237</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12813,22 +12805,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12855,13 +12847,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129483716</t>
+          <t>https://artportalen.se/Sighting/129471145</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129483958</v>
+        <v>129472963</v>
       </c>
       <c r="B101" t="n">
         <v>99118</v>
@@ -12891,7 +12883,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12904,14 +12896,14 @@
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarlsmyren, Lögkarlsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>513251</v>
+        <v>513140</v>
       </c>
       <c r="R101" t="n">
-        <v>6733203</v>
+        <v>6733188</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12938,22 +12930,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12980,13 +12972,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129483958</t>
+          <t>https://artportalen.se/Sighting/129472963</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129606047</v>
+        <v>129483716</v>
       </c>
       <c r="B102" t="n">
         <v>99118</v>
@@ -13016,26 +13008,30 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>513186</v>
+        <v>513273</v>
       </c>
       <c r="R102" t="n">
-        <v>6733152</v>
+        <v>6733194</v>
       </c>
       <c r="S102" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13059,22 +13055,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13090,24 +13086,24 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129606047</t>
+          <t>https://artportalen.se/Sighting/129483716</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129606368</v>
+        <v>129483958</v>
       </c>
       <c r="B103" t="n">
         <v>99118</v>
@@ -13137,26 +13133,30 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>513157</v>
+        <v>513251</v>
       </c>
       <c r="R103" t="n">
-        <v>6733109</v>
+        <v>6733203</v>
       </c>
       <c r="S103" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13180,22 +13180,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13211,24 +13211,24 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129606368</t>
+          <t>https://artportalen.se/Sighting/129483958</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129606685</v>
+        <v>129606047</v>
       </c>
       <c r="B104" t="n">
         <v>99118</v>
@@ -13258,7 +13258,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J104" t="inlineStr"/>
@@ -13271,10 +13271,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>513156</v>
+        <v>513186</v>
       </c>
       <c r="R104" t="n">
-        <v>6733118</v>
+        <v>6733152</v>
       </c>
       <c r="S104" t="n">
         <v>1</v>
@@ -13306,7 +13306,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13343,13 +13343,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129606685</t>
+          <t>https://artportalen.se/Sighting/129606047</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129607002</v>
+        <v>129606368</v>
       </c>
       <c r="B105" t="n">
         <v>99118</v>
@@ -13392,10 +13392,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>513149</v>
+        <v>513157</v>
       </c>
       <c r="R105" t="n">
-        <v>6733113</v>
+        <v>6733109</v>
       </c>
       <c r="S105" t="n">
         <v>1</v>
@@ -13427,7 +13427,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13464,13 +13464,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129607002</t>
+          <t>https://artportalen.se/Sighting/129606368</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129607050</v>
+        <v>129606685</v>
       </c>
       <c r="B106" t="n">
         <v>99118</v>
@@ -13500,7 +13500,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J106" t="inlineStr"/>
@@ -13513,10 +13513,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>513148</v>
+        <v>513156</v>
       </c>
       <c r="R106" t="n">
-        <v>6733113</v>
+        <v>6733118</v>
       </c>
       <c r="S106" t="n">
         <v>1</v>
@@ -13548,7 +13548,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13585,13 +13585,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129607050</t>
+          <t>https://artportalen.se/Sighting/129606685</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129607114</v>
+        <v>129607002</v>
       </c>
       <c r="B107" t="n">
         <v>99118</v>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -13634,7 +13634,7 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>513147</v>
+        <v>513149</v>
       </c>
       <c r="R107" t="n">
         <v>6733113</v>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13706,13 +13706,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129607114</t>
+          <t>https://artportalen.se/Sighting/129607002</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129607141</v>
+        <v>129607050</v>
       </c>
       <c r="B108" t="n">
         <v>99118</v>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J108" t="inlineStr"/>
@@ -13755,7 +13755,7 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>513146</v>
+        <v>513148</v>
       </c>
       <c r="R108" t="n">
         <v>6733113</v>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13827,13 +13827,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129607141</t>
+          <t>https://artportalen.se/Sighting/129607050</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129607156</v>
+        <v>129607114</v>
       </c>
       <c r="B109" t="n">
         <v>99118</v>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J109" t="inlineStr"/>
@@ -13876,7 +13876,7 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>513145</v>
+        <v>513147</v>
       </c>
       <c r="R109" t="n">
         <v>6733113</v>
@@ -13911,7 +13911,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13921,7 +13921,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13948,13 +13948,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129607156</t>
+          <t>https://artportalen.se/Sighting/129607114</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129607239</v>
+        <v>129607141</v>
       </c>
       <c r="B110" t="n">
         <v>99118</v>
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>513150</v>
+        <v>513146</v>
       </c>
       <c r="R110" t="n">
         <v>6733113</v>
@@ -14032,7 +14032,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14069,13 +14069,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129607239</t>
+          <t>https://artportalen.se/Sighting/129607141</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129607279</v>
+        <v>129607156</v>
       </c>
       <c r="B111" t="n">
         <v>99118</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -14118,10 +14118,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>513144</v>
+        <v>513145</v>
       </c>
       <c r="R111" t="n">
-        <v>6733115</v>
+        <v>6733113</v>
       </c>
       <c r="S111" t="n">
         <v>1</v>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14190,13 +14190,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129607279</t>
+          <t>https://artportalen.se/Sighting/129607156</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129607341</v>
+        <v>129607239</v>
       </c>
       <c r="B112" t="n">
         <v>99118</v>
@@ -14226,7 +14226,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -14239,10 +14239,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>513159</v>
+        <v>513150</v>
       </c>
       <c r="R112" t="n">
-        <v>6733071</v>
+        <v>6733113</v>
       </c>
       <c r="S112" t="n">
         <v>1</v>
@@ -14274,7 +14274,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14311,13 +14311,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129607341</t>
+          <t>https://artportalen.se/Sighting/129607239</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129607516</v>
+        <v>129607279</v>
       </c>
       <c r="B113" t="n">
         <v>99118</v>
@@ -14347,7 +14347,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
@@ -14360,10 +14360,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>513159</v>
+        <v>513144</v>
       </c>
       <c r="R113" t="n">
-        <v>6733070</v>
+        <v>6733115</v>
       </c>
       <c r="S113" t="n">
         <v>1</v>
@@ -14395,7 +14395,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14405,7 +14405,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14432,13 +14432,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129607516</t>
+          <t>https://artportalen.se/Sighting/129607279</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129667937</v>
+        <v>129607341</v>
       </c>
       <c r="B114" t="n">
         <v>99118</v>
@@ -14468,27 +14468,23 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
         <v>513159</v>
       </c>
       <c r="R114" t="n">
-        <v>6733165</v>
+        <v>6733071</v>
       </c>
       <c r="S114" t="n">
         <v>1</v>
@@ -14515,27 +14511,22 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Utspridd</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14551,24 +14542,24 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129667937</t>
+          <t>https://artportalen.se/Sighting/129607341</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129668007</v>
+        <v>129607516</v>
       </c>
       <c r="B115" t="n">
         <v>99118</v>
@@ -14598,7 +14589,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J115" t="inlineStr"/>
@@ -14607,14 +14598,14 @@
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>513154</v>
+        <v>513159</v>
       </c>
       <c r="R115" t="n">
-        <v>6733173</v>
+        <v>6733070</v>
       </c>
       <c r="S115" t="n">
         <v>1</v>
@@ -14641,22 +14632,22 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14672,24 +14663,24 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129668007</t>
+          <t>https://artportalen.se/Sighting/129607516</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129668091</v>
+        <v>129667937</v>
       </c>
       <c r="B116" t="n">
         <v>99118</v>
@@ -14719,10 +14710,14 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
@@ -14732,10 +14727,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>513137</v>
+        <v>513159</v>
       </c>
       <c r="R116" t="n">
-        <v>6733173</v>
+        <v>6733165</v>
       </c>
       <c r="S116" t="n">
         <v>1</v>
@@ -14767,7 +14762,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14777,7 +14772,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Utspridd</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14804,13 +14804,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129668091</t>
+          <t>https://artportalen.se/Sighting/129667937</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129668098</v>
+        <v>129668007</v>
       </c>
       <c r="B117" t="n">
         <v>99118</v>
@@ -14840,7 +14840,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
@@ -14853,10 +14853,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>513138</v>
+        <v>513154</v>
       </c>
       <c r="R117" t="n">
-        <v>6733170</v>
+        <v>6733173</v>
       </c>
       <c r="S117" t="n">
         <v>1</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14898,7 +14898,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14925,13 +14925,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129668098</t>
+          <t>https://artportalen.se/Sighting/129668007</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129668148</v>
+        <v>129668091</v>
       </c>
       <c r="B118" t="n">
         <v>99118</v>
@@ -14970,14 +14970,14 @@
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Lögkarlsmyren, Lögkarlsmyren, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>513146</v>
+        <v>513137</v>
       </c>
       <c r="R118" t="n">
-        <v>6733197</v>
+        <v>6733173</v>
       </c>
       <c r="S118" t="n">
         <v>1</v>
@@ -15009,7 +15009,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15019,7 +15019,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15046,13 +15046,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129668148</t>
+          <t>https://artportalen.se/Sighting/129668091</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129668272</v>
+        <v>129668098</v>
       </c>
       <c r="B119" t="n">
         <v>99118</v>
@@ -15082,14 +15082,10 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
@@ -15099,10 +15095,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>513125</v>
+        <v>513138</v>
       </c>
       <c r="R119" t="n">
-        <v>6733184</v>
+        <v>6733170</v>
       </c>
       <c r="S119" t="n">
         <v>1</v>
@@ -15134,7 +15130,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15144,7 +15140,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15171,13 +15167,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129668272</t>
+          <t>https://artportalen.se/Sighting/129668098</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129668456</v>
+        <v>129668148</v>
       </c>
       <c r="B120" t="n">
         <v>99118</v>
@@ -15207,27 +15203,23 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarlsmyren, Lögkarlsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>513155</v>
+        <v>513146</v>
       </c>
       <c r="R120" t="n">
-        <v>6733156</v>
+        <v>6733197</v>
       </c>
       <c r="S120" t="n">
         <v>1</v>
@@ -15259,7 +15251,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15269,7 +15261,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15296,13 +15288,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129668456</t>
+          <t>https://artportalen.se/Sighting/129668148</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129668501</v>
+        <v>129668272</v>
       </c>
       <c r="B121" t="n">
         <v>99118</v>
@@ -15332,7 +15324,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -15349,10 +15341,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>513159</v>
+        <v>513125</v>
       </c>
       <c r="R121" t="n">
-        <v>6733143</v>
+        <v>6733184</v>
       </c>
       <c r="S121" t="n">
         <v>1</v>
@@ -15384,7 +15376,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15394,7 +15386,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15421,13 +15413,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129668501</t>
+          <t>https://artportalen.se/Sighting/129668272</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129668536</v>
+        <v>129668456</v>
       </c>
       <c r="B122" t="n">
         <v>99118</v>
@@ -15457,7 +15449,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -15474,10 +15466,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>513151</v>
+        <v>513155</v>
       </c>
       <c r="R122" t="n">
-        <v>6733130</v>
+        <v>6733156</v>
       </c>
       <c r="S122" t="n">
         <v>1</v>
@@ -15509,7 +15501,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15519,12 +15511,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Klungor</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15551,13 +15538,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129668536</t>
+          <t>https://artportalen.se/Sighting/129668456</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129668673</v>
+        <v>129668501</v>
       </c>
       <c r="B123" t="n">
         <v>99118</v>
@@ -15587,7 +15574,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -15600,14 +15587,14 @@
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Lögkarlsmyren, Lögkarlsmyren, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>513184</v>
+        <v>513159</v>
       </c>
       <c r="R123" t="n">
-        <v>6733170</v>
+        <v>6733143</v>
       </c>
       <c r="S123" t="n">
         <v>1</v>
@@ -15639,7 +15626,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -15649,7 +15636,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15676,13 +15663,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129668673</t>
+          <t>https://artportalen.se/Sighting/129668501</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129668933</v>
+        <v>129668536</v>
       </c>
       <c r="B124" t="n">
         <v>99118</v>
@@ -15712,7 +15699,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -15729,13 +15716,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>513150</v>
+        <v>513151</v>
       </c>
       <c r="R124" t="n">
-        <v>6733117</v>
+        <v>6733130</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15764,7 +15751,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15774,12 +15761,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Det här området är grundligt utmärkt som Basväg med tre snitslar på kort avstånd och mellan dessa täcks av ca 500 knärotsplantor.</t>
+          <t>Klungor</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15806,13 +15793,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129668933</t>
+          <t>https://artportalen.se/Sighting/129668536</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129669000</v>
+        <v>129668673</v>
       </c>
       <c r="B125" t="n">
         <v>99118</v>
@@ -15842,7 +15829,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -15855,14 +15842,14 @@
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarlsmyren, Lögkarlsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>513155</v>
+        <v>513184</v>
       </c>
       <c r="R125" t="n">
-        <v>6733103</v>
+        <v>6733170</v>
       </c>
       <c r="S125" t="n">
         <v>1</v>
@@ -15894,7 +15881,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15904,12 +15891,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Även över dessa knärotsplantor ska basvägen gå och troligen är det planeraren har som har trampat ner plantorna när snitslarna med texten basväg sattes upp.</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15936,13 +15918,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129669000</t>
+          <t>https://artportalen.se/Sighting/129668673</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129669118</v>
+        <v>129668933</v>
       </c>
       <c r="B126" t="n">
         <v>99118</v>
@@ -15972,7 +15954,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15989,13 +15971,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>513155</v>
+        <v>513150</v>
       </c>
       <c r="R126" t="n">
-        <v>6733089</v>
+        <v>6733117</v>
       </c>
       <c r="S126" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -16024,7 +16006,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -16034,7 +16016,12 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Det här området är grundligt utmärkt som Basväg med tre snitslar på kort avstånd och mellan dessa täcks av ca 500 knärotsplantor.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -16061,13 +16048,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129669118</t>
+          <t>https://artportalen.se/Sighting/129668933</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129669192</v>
+        <v>129669000</v>
       </c>
       <c r="B127" t="n">
         <v>99118</v>
@@ -16114,10 +16101,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>513144</v>
+        <v>513155</v>
       </c>
       <c r="R127" t="n">
-        <v>6733096</v>
+        <v>6733103</v>
       </c>
       <c r="S127" t="n">
         <v>1</v>
@@ -16149,7 +16136,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -16159,7 +16146,12 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Även över dessa knärotsplantor ska basvägen gå och troligen är det planeraren har som har trampat ner plantorna när snitslarna med texten basväg sattes upp.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -16186,13 +16178,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129669192</t>
+          <t>https://artportalen.se/Sighting/129669000</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129669211</v>
+        <v>129669118</v>
       </c>
       <c r="B128" t="n">
         <v>99118</v>
@@ -16222,7 +16214,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -16239,10 +16231,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>513158</v>
+        <v>513155</v>
       </c>
       <c r="R128" t="n">
-        <v>6733074</v>
+        <v>6733089</v>
       </c>
       <c r="S128" t="n">
         <v>1</v>
@@ -16274,7 +16266,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -16284,12 +16276,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Inom en radie på 1 m</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16316,13 +16303,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129669211</t>
+          <t>https://artportalen.se/Sighting/129669118</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129669294</v>
+        <v>129669192</v>
       </c>
       <c r="B129" t="n">
         <v>99118</v>
@@ -16352,7 +16339,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -16369,10 +16356,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>513156</v>
+        <v>513144</v>
       </c>
       <c r="R129" t="n">
-        <v>6733078</v>
+        <v>6733096</v>
       </c>
       <c r="S129" t="n">
         <v>1</v>
@@ -16404,7 +16391,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -16414,12 +16401,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Minst</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -16446,13 +16428,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129669294</t>
+          <t>https://artportalen.se/Sighting/129669192</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129669313</v>
+        <v>129669211</v>
       </c>
       <c r="B130" t="n">
         <v>99118</v>
@@ -16482,7 +16464,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -16502,7 +16484,7 @@
         <v>513158</v>
       </c>
       <c r="R130" t="n">
-        <v>6733078</v>
+        <v>6733074</v>
       </c>
       <c r="S130" t="n">
         <v>1</v>
@@ -16534,7 +16516,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -16544,12 +16526,12 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>uppskattat antal</t>
+          <t>Inom en radie på 1 m</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -16576,13 +16558,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129669313</t>
+          <t>https://artportalen.se/Sighting/129669211</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129669333</v>
+        <v>129669294</v>
       </c>
       <c r="B131" t="n">
         <v>99118</v>
@@ -16612,7 +16594,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -16629,10 +16611,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>513155</v>
+        <v>513156</v>
       </c>
       <c r="R131" t="n">
-        <v>6733070</v>
+        <v>6733078</v>
       </c>
       <c r="S131" t="n">
         <v>1</v>
@@ -16664,7 +16646,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -16674,12 +16656,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>blomstänglar</t>
+          <t>Minst</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16706,13 +16688,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129669333</t>
+          <t>https://artportalen.se/Sighting/129669294</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129669372</v>
+        <v>129669313</v>
       </c>
       <c r="B132" t="n">
         <v>99118</v>
@@ -16742,7 +16724,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -16762,7 +16744,7 @@
         <v>513158</v>
       </c>
       <c r="R132" t="n">
-        <v>6733077</v>
+        <v>6733078</v>
       </c>
       <c r="S132" t="n">
         <v>1</v>
@@ -16794,7 +16776,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -16804,12 +16786,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Torvmosse, relativt öppet bland lingonris,renlav och mossa på norrsidan av en sten in mot skog. Gamla tallar, ev brandpräglade, kontinuitetsskog, inslag av gamla granar, alar, björk, skvattram och lägre buskar m.fl. i olika åldrar. Kalkbarrskog.</t>
+          <t>uppskattat antal</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16822,16 +16804,6 @@
       <c r="AG132" t="b">
         <v>0</v>
       </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>Våtmark</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>Torvmosse, relativt öppet bland lingonris,renlav och mossa på norrsidan av en sten in mot skog. Gamla tallar, ev brandpräglade, kontinuitetsskog, inslag av gamla granar, alar, björk, skvattram och lägre buskar m.fl. i olika åldrar. Kalkbarrskog.</t>
-        </is>
-      </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
@@ -16846,54 +16818,66 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129669372</t>
+          <t>https://artportalen.se/Sighting/129669313</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129440979</v>
+        <v>129669333</v>
       </c>
       <c r="B133" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>513382</v>
+        <v>513155</v>
       </c>
       <c r="R133" t="n">
-        <v>6733217</v>
+        <v>6733070</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16917,22 +16901,27 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>blomstänglar</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16941,6 +16930,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -16958,54 +16948,66 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129440979</t>
+          <t>https://artportalen.se/Sighting/129669333</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129443245</v>
+        <v>129669372</v>
       </c>
       <c r="B134" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>513373</v>
+        <v>513158</v>
       </c>
       <c r="R134" t="n">
-        <v>6733112</v>
+        <v>6733077</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -17029,22 +17031,27 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Torvmosse, relativt öppet bland lingonris,renlav och mossa på norrsidan av en sten in mot skog. Gamla tallar, ev brandpräglade, kontinuitetsskog, inslag av gamla granar, alar, björk, skvattram och lägre buskar m.fl. i olika åldrar. Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -17053,8 +17060,19 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>Våtmark</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>Torvmosse, relativt öppet bland lingonris,renlav och mossa på norrsidan av en sten in mot skog. Gamla tallar, ev brandpräglade, kontinuitetsskog, inslag av gamla granar, alar, björk, skvattram och lägre buskar m.fl. i olika åldrar. Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
@@ -17070,13 +17088,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129443245</t>
+          <t>https://artportalen.se/Sighting/129669372</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129482646</v>
+        <v>129440979</v>
       </c>
       <c r="B135" t="n">
         <v>97983</v>
@@ -17111,10 +17129,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>513277</v>
+        <v>513382</v>
       </c>
       <c r="R135" t="n">
-        <v>6733228</v>
+        <v>6733217</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -17141,22 +17159,22 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -17182,13 +17200,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129482646</t>
+          <t>https://artportalen.se/Sighting/129440979</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129483410</v>
+        <v>129443245</v>
       </c>
       <c r="B136" t="n">
         <v>97983</v>
@@ -17216,29 +17234,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>513278</v>
+        <v>513373</v>
       </c>
       <c r="R136" t="n">
-        <v>6733202</v>
+        <v>6733112</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -17265,27 +17271,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Hällartad mark.</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -17294,7 +17295,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -17312,13 +17312,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129483410</t>
+          <t>https://artportalen.se/Sighting/129443245</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129538294</v>
+        <v>129482646</v>
       </c>
       <c r="B137" t="n">
         <v>97983</v>
@@ -17349,14 +17349,14 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>513381</v>
+        <v>513277</v>
       </c>
       <c r="R137" t="n">
-        <v>6733109</v>
+        <v>6733228</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -17383,22 +17383,22 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -17424,13 +17424,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129538294</t>
+          <t>https://artportalen.se/Sighting/129482646</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129538564</v>
+        <v>129483410</v>
       </c>
       <c r="B138" t="n">
         <v>97983</v>
@@ -17458,21 +17458,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>513384</v>
+        <v>513278</v>
       </c>
       <c r="R138" t="n">
-        <v>6733132</v>
+        <v>6733202</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -17499,27 +17507,27 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Runt tallen i mitten på bilden på andra sidan bäcken.</t>
+          <t>Hällartad mark.</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -17546,13 +17554,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129538564</t>
+          <t>https://artportalen.se/Sighting/129483410</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129540902</v>
+        <v>129538294</v>
       </c>
       <c r="B139" t="n">
         <v>97983</v>
@@ -17581,20 +17589,16 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>513279</v>
+        <v>513381</v>
       </c>
       <c r="R139" t="n">
-        <v>6733141</v>
+        <v>6733109</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17626,7 +17630,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -17636,12 +17640,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>16:42</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Fläckvis på trädens socklar i kärret. Det är omöjligt att avgöra vad man missar i mörker med pannlampa. bäcken är inte så bred med kärret men är ca 30-40 meter brett mellan kullarna.</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17650,7 +17649,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -17668,13 +17666,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129540902</t>
+          <t>https://artportalen.se/Sighting/129538294</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129668693</v>
+        <v>129538564</v>
       </c>
       <c r="B140" t="n">
         <v>97983</v>
@@ -17702,32 +17700,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Lögkarlsmyren, Lögkarlsmyren, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>513186</v>
+        <v>513384</v>
       </c>
       <c r="R140" t="n">
-        <v>6733166</v>
+        <v>6733132</v>
       </c>
       <c r="S140" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -17751,22 +17741,27 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Runt tallen i mitten på bilden på andra sidan bäcken.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17792,6 +17787,253 @@
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129538564</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>129540902</v>
+      </c>
+      <c r="B141" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>513279</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6733141</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Fläckvis på trädens socklar i kärret. Det är omöjligt att avgöra vad man missar i mörker med pannlampa. bäcken är inte så bred med kärret men är ca 30-40 meter brett mellan kullarna.</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF141" t="inlineStr"/>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129540902</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>129668693</v>
+      </c>
+      <c r="B142" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Lögkarlsmyren, Lögkarlsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>513186</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6733166</v>
+      </c>
+      <c r="S142" t="n">
+        <v>1</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129668693</t>
         </is>
@@ -17938,6 +18180,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>136801931</v>
       </c>
       <c r="B4" t="n">
-        <v>97624</v>
+        <v>97626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>136801921</v>
       </c>
       <c r="B15" t="n">
-        <v>91887</v>
+        <v>91889</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>136801933</v>
       </c>
       <c r="B16" t="n">
-        <v>91887</v>
+        <v>91889</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>136801945</v>
       </c>
       <c r="B28" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>136801947</v>
       </c>
       <c r="B32" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>136801928</v>
       </c>
       <c r="B48" t="n">
-        <v>93393</v>
+        <v>93395</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>136801912</v>
       </c>
       <c r="B92" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>136801906</v>
       </c>
       <c r="B93" t="n">
-        <v>111330</v>
+        <v>111332</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>136801949</v>
       </c>
       <c r="B94" t="n">
-        <v>111330</v>
+        <v>111332</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>136801956</v>
       </c>
       <c r="B95" t="n">
-        <v>111330</v>
+        <v>111332</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>136801948</v>
       </c>
       <c r="B148" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>136801920</v>
       </c>
       <c r="B157" t="n">
-        <v>103928</v>
+        <v>103930</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>136801904</v>
       </c>
       <c r="B158" t="n">
-        <v>104071</v>
+        <v>104073</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>136801921</v>
       </c>
       <c r="B14" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>136801933</v>
       </c>
       <c r="B15" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136801945</v>
       </c>
       <c r="B27" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>136801947</v>
       </c>
       <c r="B31" t="n">
-        <v>93431</v>
+        <v>93433</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>136801928</v>
       </c>
       <c r="B47" t="n">
-        <v>93397</v>
+        <v>93399</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>136801912</v>
       </c>
       <c r="B91" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>136801906</v>
       </c>
       <c r="B92" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>136801949</v>
       </c>
       <c r="B93" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>136801956</v>
       </c>
       <c r="B94" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>136801948</v>
       </c>
       <c r="B147" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>136801920</v>
       </c>
       <c r="B156" t="n">
-        <v>103936</v>
+        <v>103938</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>136801904</v>
       </c>
       <c r="B157" t="n">
-        <v>104079</v>
+        <v>104081</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -11648,7 +11648,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -11760,7 +11760,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>136801921</v>
       </c>
       <c r="B14" t="n">
-        <v>91893</v>
+        <v>91894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2274,7 +2274,7 @@
         <v>136801933</v>
       </c>
       <c r="B15" t="n">
-        <v>91893</v>
+        <v>91894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -3793,7 +3793,7 @@
         <v>136801945</v>
       </c>
       <c r="B27" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>136801947</v>
       </c>
       <c r="B31" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>136801928</v>
       </c>
       <c r="B47" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -11551,7 +11551,7 @@
         <v>136801912</v>
       </c>
       <c r="B91" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -11663,7 +11663,7 @@
         <v>136801906</v>
       </c>
       <c r="B92" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -11775,7 +11775,7 @@
         <v>136801949</v>
       </c>
       <c r="B93" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>136801956</v>
       </c>
       <c r="B94" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>136801948</v>
       </c>
       <c r="B147" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>136801920</v>
       </c>
       <c r="B156" t="n">
-        <v>103938</v>
+        <v>103939</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -19685,7 +19685,7 @@
         <v>136801904</v>
       </c>
       <c r="B157" t="n">
-        <v>104081</v>
+        <v>104082</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>136801921</v>
       </c>
       <c r="B14" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>136801933</v>
       </c>
       <c r="B15" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136801945</v>
       </c>
       <c r="B27" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>136801947</v>
       </c>
       <c r="B31" t="n">
-        <v>93434</v>
+        <v>93440</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>136801928</v>
       </c>
       <c r="B47" t="n">
-        <v>93400</v>
+        <v>93406</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>136801912</v>
       </c>
       <c r="B91" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>136801906</v>
       </c>
       <c r="B92" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>136801949</v>
       </c>
       <c r="B93" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>136801956</v>
       </c>
       <c r="B94" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>136801948</v>
       </c>
       <c r="B147" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>136801920</v>
       </c>
       <c r="B156" t="n">
-        <v>103939</v>
+        <v>103945</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>136801904</v>
       </c>
       <c r="B157" t="n">
-        <v>104082</v>
+        <v>104088</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>136801921</v>
       </c>
       <c r="B14" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>136801933</v>
       </c>
       <c r="B15" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136801945</v>
       </c>
       <c r="B27" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>136801947</v>
       </c>
       <c r="B31" t="n">
-        <v>93440</v>
+        <v>93444</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>136801928</v>
       </c>
       <c r="B47" t="n">
-        <v>93406</v>
+        <v>93410</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>136801912</v>
       </c>
       <c r="B91" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>136801906</v>
       </c>
       <c r="B92" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>136801949</v>
       </c>
       <c r="B93" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>136801956</v>
       </c>
       <c r="B94" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>136801948</v>
       </c>
       <c r="B147" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>136801920</v>
       </c>
       <c r="B156" t="n">
-        <v>103945</v>
+        <v>103949</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>136801904</v>
       </c>
       <c r="B157" t="n">
-        <v>104088</v>
+        <v>104092</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>136801921</v>
       </c>
       <c r="B14" t="n">
-        <v>91919</v>
+        <v>91921</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>136801933</v>
       </c>
       <c r="B15" t="n">
-        <v>91919</v>
+        <v>91921</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136801945</v>
       </c>
       <c r="B27" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>136801947</v>
       </c>
       <c r="B31" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>136801928</v>
       </c>
       <c r="B47" t="n">
-        <v>93425</v>
+        <v>93426</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>136801934</v>
       </c>
       <c r="B57" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>136801938</v>
       </c>
       <c r="B65" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>136520715</v>
       </c>
       <c r="B79" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>136801941</v>
       </c>
       <c r="B89" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>136525638</v>
       </c>
       <c r="B90" t="n">
-        <v>58885</v>
+        <v>58887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>136801912</v>
       </c>
       <c r="B91" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>136801906</v>
       </c>
       <c r="B92" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>136801949</v>
       </c>
       <c r="B93" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>136801956</v>
       </c>
       <c r="B94" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>136801948</v>
       </c>
       <c r="B147" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>136801920</v>
       </c>
       <c r="B156" t="n">
-        <v>103966</v>
+        <v>103968</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>136801904</v>
       </c>
       <c r="B157" t="n">
-        <v>104109</v>
+        <v>104111</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -10144,11 +10144,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
@@ -11460,11 +11456,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
@@ -18522,11 +18514,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>136801921</v>
       </c>
       <c r="B14" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>136801933</v>
       </c>
       <c r="B15" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136801945</v>
       </c>
       <c r="B27" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>136801947</v>
       </c>
       <c r="B31" t="n">
-        <v>93460</v>
+        <v>93463</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>136801928</v>
       </c>
       <c r="B47" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>136801912</v>
       </c>
       <c r="B91" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>136801906</v>
       </c>
       <c r="B92" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         <v>136801949</v>
       </c>
       <c r="B93" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>136801956</v>
       </c>
       <c r="B94" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>136801948</v>
       </c>
       <c r="B147" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>136801920</v>
       </c>
       <c r="B156" t="n">
-        <v>103968</v>
+        <v>103971</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>136801904</v>
       </c>
       <c r="B157" t="n">
-        <v>104111</v>
+        <v>104114</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>136801921</v>
       </c>
       <c r="B14" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>136801933</v>
       </c>
       <c r="B15" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136801945</v>
       </c>
       <c r="B27" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>136801947</v>
       </c>
       <c r="B31" t="n">
-        <v>93463</v>
+        <v>93473</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>136801928</v>
       </c>
       <c r="B47" t="n">
-        <v>93429</v>
+        <v>93439</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>136801934</v>
       </c>
       <c r="B57" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>136801938</v>
       </c>
       <c r="B65" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         <v>136801941</v>
       </c>
       <c r="B89" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>136801912</v>
       </c>
       <c r="B91" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>136801906</v>
       </c>
       <c r="B92" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         <v>136801949</v>
       </c>
       <c r="B93" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>136801956</v>
       </c>
       <c r="B94" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>136801948</v>
       </c>
       <c r="B147" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>136801920</v>
       </c>
       <c r="B156" t="n">
-        <v>103971</v>
+        <v>103986</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>136801904</v>
       </c>
       <c r="B157" t="n">
-        <v>104114</v>
+        <v>104129</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>136801921</v>
       </c>
       <c r="B14" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>136801933</v>
       </c>
       <c r="B15" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136801945</v>
       </c>
       <c r="B27" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>136801947</v>
       </c>
       <c r="B31" t="n">
-        <v>93473</v>
+        <v>93474</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>136801928</v>
       </c>
       <c r="B47" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>136801912</v>
       </c>
       <c r="B91" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>136801906</v>
       </c>
       <c r="B92" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         <v>136801949</v>
       </c>
       <c r="B93" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>136801956</v>
       </c>
       <c r="B94" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>136801948</v>
       </c>
       <c r="B147" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>136801920</v>
       </c>
       <c r="B156" t="n">
-        <v>103986</v>
+        <v>103987</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>136801904</v>
       </c>
       <c r="B157" t="n">
-        <v>104129</v>
+        <v>104130</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>136801921</v>
       </c>
       <c r="B14" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>136801933</v>
       </c>
       <c r="B15" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136801945</v>
       </c>
       <c r="B27" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>136801947</v>
       </c>
       <c r="B31" t="n">
-        <v>93474</v>
+        <v>93479</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>136801928</v>
       </c>
       <c r="B47" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>136801934</v>
       </c>
       <c r="B57" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>136801938</v>
       </c>
       <c r="B65" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>136801912</v>
       </c>
       <c r="B91" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>136801906</v>
       </c>
       <c r="B92" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         <v>136801949</v>
       </c>
       <c r="B93" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>136801956</v>
       </c>
       <c r="B94" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>136801948</v>
       </c>
       <c r="B147" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>136801920</v>
       </c>
       <c r="B156" t="n">
-        <v>103987</v>
+        <v>103992</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>136801904</v>
       </c>
       <c r="B157" t="n">
-        <v>104130</v>
+        <v>104135</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>136801921</v>
       </c>
       <c r="B14" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>136801933</v>
       </c>
       <c r="B15" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136801945</v>
       </c>
       <c r="B27" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>136801947</v>
       </c>
       <c r="B31" t="n">
-        <v>93479</v>
+        <v>93481</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>136801928</v>
       </c>
       <c r="B47" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>136801912</v>
       </c>
       <c r="B91" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>136801906</v>
       </c>
       <c r="B92" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         <v>136801949</v>
       </c>
       <c r="B93" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>136801956</v>
       </c>
       <c r="B94" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>136801948</v>
       </c>
       <c r="B147" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>136801920</v>
       </c>
       <c r="B156" t="n">
-        <v>103992</v>
+        <v>103995</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>136801904</v>
       </c>
       <c r="B157" t="n">
-        <v>104135</v>
+        <v>104138</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -2153,7 +2153,7 @@
         <v>136801921</v>
       </c>
       <c r="B14" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>136801933</v>
       </c>
       <c r="B15" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136801945</v>
       </c>
       <c r="B27" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>136801947</v>
       </c>
       <c r="B31" t="n">
-        <v>93481</v>
+        <v>93487</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>136801928</v>
       </c>
       <c r="B47" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>136801934</v>
       </c>
       <c r="B57" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>136801912</v>
       </c>
       <c r="B91" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>136801906</v>
       </c>
       <c r="B92" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         <v>136801949</v>
       </c>
       <c r="B93" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>136801956</v>
       </c>
       <c r="B94" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>136801948</v>
       </c>
       <c r="B147" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>136801920</v>
       </c>
       <c r="B156" t="n">
-        <v>103995</v>
+        <v>104001</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>136801904</v>
       </c>
       <c r="B157" t="n">
-        <v>104138</v>
+        <v>104144</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/S 1500-2025 artfynd.xlsx
+++ b/artfynd/S 1500-2025 artfynd.xlsx
@@ -11655,7 +11655,7 @@
         <v>136801906</v>
       </c>
       <c r="B92" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>136801920</v>
       </c>
       <c r="B156" t="n">
-        <v>104001</v>
+        <v>104002</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
